--- a/images/document/BA DOC/Danh_Sach_Kich_Ban_Thong_Bao_Notification_VNA.xlsx
+++ b/images/document/BA DOC/Danh_Sach_Kich_Ban_Thong_Bao_Notification_VNA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d39b8747432be571/Work/04. Company/Synodus/GOV/01.VNA/VNA/images/document/BA DOC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_91D5F4550C10B60D44D201099ADADE32D605328B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F965CB2E-2E19-E34D-A201-C98D5D5C7CEE}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_93ADAED65B0A42C7C80014FF7B59782981560B81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39C608F0-FBAC-5B40-93F2-2D9938FBE71E}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="500" windowWidth="33720" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4180" yWindow="500" windowWidth="29420" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Danh Mục Tổng Hợp" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="246">
   <si>
     <t>TỔNG CÔNG TY HÀNG KHÔNG VIỆT NAM (VIETNAM AIRLINES) - CỔNG THÔNG TIN NET ZERO &amp; BÁO CÁO PHÁT TRIỂN BỀN VỮNG</t>
   </si>
@@ -235,6 +235,36 @@
     <t>Điều hướng đến Điều chỉnh số liệu công bố -&gt; Chọn chỉ tiêu {indicator_code} -&gt; Tab Quản lý phiên bản</t>
   </si>
   <si>
+    <t>NOTIF-CMS-004</t>
+  </si>
+  <si>
+    <t>CMS - Quản lý Biểu đồ Công bố &amp; Điều chỉnh số liệu</t>
+  </si>
+  <si>
+    <t>CMS Admin từ chối thẻ yêu cầu công bố tại Backlog kèm lý do từ chối</t>
+  </si>
+  <si>
+    <t>CMS Admin bấm nút icon Từ chối (XCircle) tại hàng biểu đồ trong Backlog CMS, nhập "Lý do từ chối" vào popup và bấm "Xác nhận từ chối"</t>
+  </si>
+  <si>
+    <t>Quản trị viên CMS (Admin / Ban KHPT)</t>
+  </si>
+  <si>
+    <t>Chuyên viên / User Tổ ban đã bấm "Đề nghị công bố" thẻ yêu cầu đó (Người gửi đề xuất)</t>
+  </si>
+  <si>
+    <t>[Từ chối công bố] {indicator_code} - {chart_name}</t>
+  </si>
+  <si>
+    <t>Yêu cầu công bố biểu đồ "{chart_name}" (Chỉ tiêu {indicator_code}) của bạn đã bị từ chối bởi {admin_name}. Lý do: "{reject_reason}". Vui lòng kiểm tra và hiệu chỉnh lại số liệu.</t>
+  </si>
+  <si>
+    <t>Chuyển tới Điều chỉnh số liệu công bố -&gt; Tự động chọn chỉ tiêu {indicator_code} -&gt; Mở tab Quản lý phiên bản và hiển thị chi tiết lý do từ chối</t>
+  </si>
+  <si>
+    <t>In-app Quả chuông, Toast popup, Email</t>
+  </si>
+  <si>
     <t>NOTIF-ADJ-003</t>
   </si>
   <si>
@@ -292,9 +322,156 @@
     <t>In-app Quả chuông, Toast khẩn cấp, Email</t>
   </si>
   <si>
+    <t>NOTIF-DOC-004</t>
+  </si>
+  <si>
+    <t>Phê duyệt tài liệu đưa vào Kho lưu trữ chung thành công</t>
+  </si>
+  <si>
+    <t>Người kiểm duyệt nhấn "Phê duyệt" tài liệu tại màn hình Phê duyệt tài liệu (DocumentApproval.tsx)</t>
+  </si>
+  <si>
+    <t>Người kiểm duyệt tài liệu (Ban KHPT / Admin)</t>
+  </si>
+  <si>
+    <t>Người tải lên tài liệu (Uploader)</t>
+  </si>
+  <si>
+    <t>[Phê duyệt tài liệu] Tài liệu "{doc_name}" đã được duyệt vào Kho tài liệu PTBV</t>
+  </si>
+  <si>
+    <t>Tài liệu "{doc_name}" (Mã: {doc_code}) gửi ngày {submit_date} đã được {approver_name} phê duyệt thành công và đưa vào Kho tài liệu PTBV chung.</t>
+  </si>
+  <si>
+    <t>Điều hướng đến Kho tài liệu PTBV -&gt; Xem tài liệu đã duyệt trong kho chung</t>
+  </si>
+  <si>
+    <t>In-app Quả chuông, Email xác nhận</t>
+  </si>
+  <si>
+    <t>NOTIF-DOC-006</t>
+  </si>
+  <si>
+    <t>Cập nhật phiên bản mới của tài liệu trong Kho PTBV (v1.0 -&gt; v2.0)</t>
+  </si>
+  <si>
+    <t>Người dùng tải tệp thay thế hoặc cập nhật phiên bản tài liệu mới (Semantic Versioning)</t>
+  </si>
+  <si>
+    <t>Người sở hữu tài liệu / Quản trị viên Kho</t>
+  </si>
+  <si>
+    <t>Toàn bộ cán bộ nhân viên có quyền truy cập tài liệu này</t>
+  </si>
+  <si>
+    <t>[Cập nhật phiên bản] Tài liệu "{doc_name}" đã nâng cấp lên bản {doc_version}</t>
+  </si>
+  <si>
+    <t>Tài liệu "{doc_name}" vừa được {user_name} cập nhật phiên bản mới {doc_version} (Ghi chú: {version_notes}). Nhấn để tải về tài liệu mới nhất.</t>
+  </si>
+  <si>
+    <t>Điều hướng đến Kho tài liệu PTBV -&gt; Mở modal Chi tiết tài liệu với bản mới nhất</t>
+  </si>
+  <si>
+    <t>In-app Quả chuông</t>
+  </si>
+  <si>
+    <t>Trung bình (P2)</t>
+  </si>
+  <si>
+    <t>KỊCH BẢN THÔNG BÁO THEO YÊU CẦU TRỌNG TÂM CỦA NGƯỜI DÙNG</t>
+  </si>
+  <si>
+    <t>Chi tiết 6 kịch bản thông báo chính thức tại phân hệ CMS &amp; Điều chỉnh số liệu công bố theo yêu cầu của Vietnam Airlines</t>
+  </si>
+  <si>
+    <t>Phân Hệ / Chức Năng</t>
+  </si>
+  <si>
+    <t>Yêu Cầu Từ Người Dùng</t>
+  </si>
+  <si>
+    <t>Sự Kiện Kích Hoạt (Trigger Event)</t>
+  </si>
+  <si>
+    <t>Người Thực Hiện Thao Tác</t>
+  </si>
+  <si>
+    <t>Nội Dung Hiển Thị Mẫu (In-app Notification)</t>
+  </si>
+  <si>
+    <t>Mức Độ Thông Báo</t>
+  </si>
+  <si>
+    <t>Hành Vi Khi Người Dùng Bấm Vào Thông Báo (Deep Link)</t>
+  </si>
+  <si>
+    <t>Kênh Triển Khai</t>
+  </si>
+  <si>
+    <t>Mức Độ Ưu Tiên</t>
+  </si>
+  <si>
+    <t>PHÂN TÍCH NGHIỆP VỤ &amp; ĐỀ XUẤT BỔ SUNG KỊCH BẢN THÔNG BÁO</t>
+  </si>
+  <si>
+    <t>Đánh giá rủi ro khoảng trống quy trình (Blind Spots), giá trị nghiệp vụ và giải pháp thông báo bổ trợ cho CMS &amp; Điều chỉnh số liệu</t>
+  </si>
+  <si>
+    <t>Kịch Bản Nghiệp Vụ Bổ Sung</t>
+  </si>
+  <si>
+    <t>Rủi Ro Nghiệp Vụ Nếu Thiếu Thông Báo Này (Risk / Pain Point)</t>
+  </si>
+  <si>
+    <t>Giá Trị Mang Lại Cho Vietnam Airlines (Business Value)</t>
+  </si>
+  <si>
+    <t>Hành Động Kích Hoạt &amp; Đối Tượng Nhận Tin</t>
+  </si>
+  <si>
+    <t>Nội Dung Thông Báo Đề Xuất</t>
+  </si>
+  <si>
+    <t>Mức Độ Ưu Tiên Triển Khai</t>
+  </si>
+  <si>
+    <t>Các tổ ban và bộ phận truyền thông không biết phiên bản nào đang là số liệu chính thức được phép trích xuất phục vụ kiểm toán đối ngoại.</t>
+  </si>
+  <si>
+    <t>Minh bạch hóa phiên bản dữ liệu hiện hành, đảm bảo tính duy nhất và nhất quán của số liệu công bố trên toàn hệ thống.</t>
+  </si>
+  <si>
+    <t>Admin kích hoạt bản Active -&gt; Gửi toàn bộ Tổ ban phụ trách &amp; Ban Biên tập báo cáo</t>
+  </si>
+  <si>
+    <t>Yêu cầu khẩn gỡ công bố phiên bản (Unpublish Request)</t>
+  </si>
+  <si>
+    <t>Khi phát hiện số liệu sai sót nghiêm trọng hoặc có thay đổi kiểm toán, nếu không có cơ chế báo khẩn, số liệu sai sẽ tiếp tục hiển thị đối ngoại gây khủng hoảng thông tin.</t>
+  </si>
+  <si>
+    <t>Phản ứng nhanh với sự cố sai lệch số liệu, cho phép thu hồi và tạm ẩn biểu đồ ngay lập tức để rà soát.</t>
+  </si>
+  <si>
+    <t>Tổ ban gửi yêu cầu gỡ công bố -&gt; Gửi Quản trị viên CMS &amp; Lãnh đạo Ban KHPT</t>
+  </si>
+  <si>
     <t>NOTIF-ADJ-005</t>
   </si>
   <si>
+    <t>Từ chối yêu cầu công bố số liệu kèm lý do</t>
+  </si>
+  <si>
+    <t>Chuyên viên tổ ban gửi yêu cầu công bố nhưng không nhận được phản hồi, không biết lý do bị chậm hoặc bị từ chối, gây tắc nghẽn tiến độ đóng kỳ báo cáo.</t>
+  </si>
+  <si>
+    <t>Khép kín chu trình kiểm duyệt (Approval Loop), giúp người nhập dữ liệu nhanh chóng sửa chữa đúng trọng tâm yêu cầu. (Đã chuẩn hóa chính thức thành kịch bản trọng tâm NOTIF-CMS-004 tại Backlog CMS &amp; Điều chỉnh số liệu).</t>
+  </si>
+  <si>
+    <t>Admin/Lãnh đạo bấm Từ chối -&gt; Gửi Chuyên viên tổ ban đã tạo yêu cầu</t>
+  </si>
+  <si>
     <t>Yêu cầu công bố phiên bản {version_number} cho biểu đồ "{chart_name}" đã bị từ chối bởi {user_name}. Lý do: "{reject_reason}". Vui lòng kiểm tra và hiệu chỉnh lại.</t>
   </si>
   <si>
@@ -304,39 +481,69 @@
     <t>Cảnh báo sai lệch số liệu nguồn so với bản đã công bố (Data Drift Alert)</t>
   </si>
   <si>
+    <t>Dữ liệu ở các phân hệ nguồn (Nhập liệu thủ công, ERP, Flight Data) bị ai đó sửa đổi ngầm sau khi đã công bố, dẫn đến số liệu công bố vênh với số liệu sổ sách kế toán.</t>
+  </si>
+  <si>
+    <t>Tự động phát hiện bất đồng bộ dữ liệu (Data Integrity Audit), bảo vệ tính pháp lý của báo cáo thường niên.</t>
+  </si>
+  <si>
+    <t>Hệ thống tự động phát hiện lệch -&gt; Gửi Chuyên viên phụ trách chỉ tiêu &amp; Quản trị viên số liệu</t>
+  </si>
+  <si>
     <t>Phát hiện số liệu gốc kỳ {period} của chỉ tiêu "{indicator_name}" vừa được cập nhật tại Form nhập liệu, có chênh lệch so với bản công bố {version_number}. Vui lòng rà soát lại.</t>
   </si>
   <si>
-    <t>Trung bình (P2)</t>
-  </si>
-  <si>
     <t>NOTIF-ADJ-007</t>
   </si>
   <si>
     <t>Cập nhật nội dung Thuyết minh công bố định tính của biểu đồ</t>
   </si>
   <si>
+    <t>Thuyết minh giải trình biến động (GRI Disclosure) bị cập nhật nhưng các bên liên quan không nắm được ngữ cảnh phân tích mới.</t>
+  </si>
+  <si>
+    <t>Đồng bộ hóa thông điệp truyền thông giữa số liệu biểu đồ và văn bản phân tích nguyên nhân tăng giảm phát thải.</t>
+  </si>
+  <si>
+    <t>Biên tập viên lưu thuyết minh -&gt; Gửi các Tổ ban liên quan &amp; Ban Truyền thông</t>
+  </si>
+  <si>
     <t>{user_name} vừa cập nhật nội dung thuyết minh công bố cho biểu đồ "{chart_name}" (Chỉ tiêu {indicator_code}) theo phiên bản {version_number}.</t>
   </si>
   <si>
-    <t>In-app Quả chuông</t>
-  </si>
-  <si>
     <t>NOTIF-ADJ-008</t>
   </si>
   <si>
     <t>Nhắc nhở định kỳ rà soát &amp; cập nhật phiên bản số liệu công bố</t>
   </si>
   <si>
+    <t>Các đơn vị chậm trễ nộp báo cáo định kỳ tháng/quý dẫn đến việc cổng Net Zero bị chậm tiến độ cập nhật số liệu mới cho cổ đông và nhà đầu tư.</t>
+  </si>
+  <si>
+    <t>Tự động hóa quy trình đôn đốc tiến độ, giảm thiểu thời gian nhân sự quản trị phải đi nhắc việc thủ công.</t>
+  </si>
+  <si>
+    <t>Hệ thống tự động nhắc ngày 25 hàng tháng -&gt; Gửi Đầu mối nhập liệu của các Tổ ban</t>
+  </si>
+  <si>
     <t>Đã đến kỳ rà soát dữ liệu công bố {period}. Vui lòng kiểm tra số liệu các chỉ tiêu được phân công và tạo phiên bản công bố mới trước ngày {deadline}.</t>
   </si>
   <si>
-    <t>NOTIF-CMS-004</t>
+    <t>NOTIF-CMS-007</t>
   </si>
   <si>
     <t>Sắp xếp lại thứ tự hiển thị biểu đồ trên Trang chi tiết Trụ cột</t>
   </si>
   <si>
+    <t>Thay đổi vị trí biểu đồ trọng điểm vô tình làm đảo lộn cấu trúc logic của báo cáo chuyên môn mà ban phụ trách trụ cột không hay biết.</t>
+  </si>
+  <si>
+    <t>Lưu vết và thông báo thay đổi layout giao diện, giúp ban phụ trách kiểm soát thứ tự ưu tiên truyền thông.</t>
+  </si>
+  <si>
+    <t>Admin kéo thả đổi thứ tự biểu đồ -&gt; Gửi Ban phụ trách Trụ cột &amp; Ban Truyền thông</t>
+  </si>
+  <si>
     <t>{user_name} vừa điều chỉnh lại thứ tự hiển thị của {count} biểu đồ thuộc Trụ cột {pillar_name} trên trang chi tiết công bố.</t>
   </si>
   <si>
@@ -352,6 +559,15 @@
     <t>Kích hoạt xuất bản toàn diện Cổng thông tin Net Zero / Báo cáo ESG</t>
   </si>
   <si>
+    <t>Hệ thống đã cập nhật bộ số liệu mới ra ngoài cổng thông tin công cộng nhưng nội bộ cán bộ công nhân viên không nắm được để truyền thông thống nhất.</t>
+  </si>
+  <si>
+    <t>Tạo sự đồng thuận cao, thông tin kịp thời đến toàn bộ Tổng công ty về thành tựu và chỉ số Net Zero mới nhất.</t>
+  </si>
+  <si>
+    <t>Lãnh đạo bấm Xuất bản Portal -&gt; Gửi Toàn thể người dùng hệ thống ESG VNA</t>
+  </si>
+  <si>
     <t>Cổng thông tin Net Zero &amp; Báo cáo Phát triển bền vững Vietnam Airlines đã chính thức xuất bản phiên bản {portal_version}. Nhấn để xem trang chủ công bố.</t>
   </si>
   <si>
@@ -361,31 +577,25 @@
     <t>Cảnh báo Biểu đồ xuất bản bị khuyết thiếu dữ liệu kỳ báo cáo mới</t>
   </si>
   <si>
+    <t>Biểu đồ được xuất bản công khai ra ngoài nhưng bị trắng số liệu (Blank chart) hoặc chỉ có dữ liệu cũ của năm ngoái, ảnh hưởng hình ảnh chuyên nghiệp của VNA.</t>
+  </si>
+  <si>
+    <t>Ngăn chặn lỗi hiển thị biểu đồ rỗng trên cổng thông tin đối ngoại, đóng vai trò như chốt kiểm soát chất lượng (Quality Gate).</t>
+  </si>
+  <si>
+    <t>Hệ thống phát hiện thiếu số liệu -&gt; Gửi Quản trị viên CMS &amp; Tổ ban liên quan</t>
+  </si>
+  <si>
     <t>Biểu đồ "{chart_name}" đang được đính kèm xuất bản nhưng chưa có dữ liệu kỳ {period} hoặc chưa có phiên bản Active. Vui lòng bổ sung trước khi xuất bản.</t>
   </si>
   <si>
-    <t>NOTIF-DOC-004</t>
-  </si>
-  <si>
-    <t>Phê duyệt tài liệu đưa vào Kho lưu trữ chung thành công</t>
-  </si>
-  <si>
-    <t>Người kiểm duyệt nhấn "Phê duyệt" tài liệu tại màn hình Phê duyệt tài liệu (DocumentApproval.tsx)</t>
-  </si>
-  <si>
-    <t>Người kiểm duyệt tài liệu (Ban KHPT / Admin)</t>
-  </si>
-  <si>
-    <t>Người tải lên tài liệu (Uploader)</t>
-  </si>
-  <si>
-    <t>Tài liệu "{doc_name}" (Mã: {doc_code}) gửi ngày {submit_date} đã được {approver_name} phê duyệt thành công và đưa vào Kho tài liệu PTBV chung.</t>
-  </si>
-  <si>
-    <t>Điều hướng đến Kho tài liệu PTBV -&gt; Xem tài liệu đã duyệt trong kho chung</t>
-  </si>
-  <si>
-    <t>In-app Quả chuông, Email xác nhận</t>
+    <t>Người đăng tải không biết tài liệu đã được duyệt hay chưa, dẫn đến việc tải lên trùng lặp hoặc không kịp thời chia sẻ cho đối tác.</t>
+  </si>
+  <si>
+    <t>Rút ngắn vòng quay tài liệu, giúp người nộp tài liệu an tâm rằng văn bản đã được pháp chế/Ban KHPT công nhận lưu kho.</t>
+  </si>
+  <si>
+    <t>Người kiểm duyệt bấm Phê duyệt -&gt; Gửi Người đăng tải tài liệu (Uploader)</t>
   </si>
   <si>
     <t>NOTIF-DOC-005</t>
@@ -394,31 +604,25 @@
     <t>Từ chối phê duyệt tài liệu đưa vào Kho lưu trữ chung</t>
   </si>
   <si>
+    <t>Tài liệu bị treo không được duyệt mà không rõ nguyên nhân, dẫn đến thất lạc hồ sơ chứng nhận môi trường quan trọng.</t>
+  </si>
+  <si>
+    <t>Phản hồi minh bạch nguyên nhân từ chối (thiếu chữ ký số, sai định dạng, hết hạn) để đơn vị nhanh chóng hoàn thiện hồ sơ.</t>
+  </si>
+  <si>
+    <t>Người kiểm duyệt bấm Từ chối -&gt; Gửi Người đăng tải tài liệu</t>
+  </si>
+  <si>
     <t>Yêu cầu lưu kho tài liệu "{doc_name}" (Mã: {doc_code}) đã bị từ chối bởi {approver_name}. Lý do: "{reject_reason}". Vui lòng kiểm tra và gửi lại.</t>
   </si>
   <si>
-    <t>NOTIF-DOC-006</t>
-  </si>
-  <si>
-    <t>Cập nhật phiên bản mới của tài liệu trong Kho PTBV (v1.0 -&gt; v2.0)</t>
-  </si>
-  <si>
-    <t>Người dùng tải tệp thay thế hoặc cập nhật phiên bản tài liệu mới (Semantic Versioning)</t>
-  </si>
-  <si>
-    <t>Người sở hữu tài liệu / Quản trị viên Kho</t>
-  </si>
-  <si>
-    <t>Toàn bộ cán bộ nhân viên có quyền truy cập tài liệu này</t>
-  </si>
-  <si>
-    <t>[Cập nhật phiên bản] Tài liệu "{doc_name}" đã nâng cấp lên bản {doc_version}</t>
-  </si>
-  <si>
-    <t>Tài liệu "{doc_name}" vừa được {user_name} cập nhật phiên bản mới {doc_version} (Ghi chú: {version_notes}). Nhấn để tải về tài liệu mới nhất.</t>
-  </si>
-  <si>
-    <t>Điều hướng đến Kho tài liệu PTBV -&gt; Mở modal Chi tiết tài liệu với bản mới nhất</t>
+    <t>Cán bộ các ban tiếp tục sử dụng các quy chuẩn cũ, biểu mẫu cũ đã lỗi thời do không biết đã có bản cập nhật mới được ban hành.</t>
+  </si>
+  <si>
+    <t>Đảm bảo toàn bộ Tổng công ty luôn áp dụng phiên bản tài liệu chuẩn hóa mới nhất theo chuẩn quốc tế IATA/ICAO.</t>
+  </si>
+  <si>
+    <t>Người quản lý kho cập nhật phiên bản -&gt; Gửi Toàn bộ cán bộ có quyền truy cập</t>
   </si>
   <si>
     <t>NOTIF-DOC-007</t>
@@ -427,187 +631,16 @@
     <t>Yêu cầu cấp quyền truy cập tài liệu nội bộ / bảo mật</t>
   </si>
   <si>
+    <t>Tài liệu bảo mật cao bị người ngoài ban xem trái phép hoặc ngược lại chuyên viên cần dữ liệu phục vụ kiểm toán bị chậm trễ cấp quyền.</t>
+  </si>
+  <si>
+    <t>Quản trị an toàn thông tin theo chuẩn phân quyền tài liệu nội bộ, có vết phê duyệt cấp quyền rõ ràng.</t>
+  </si>
+  <si>
+    <t>User bấm Xin quyền -&gt; Gửi Người sở hữu tài liệu &amp; Admin hệ thống</t>
+  </si>
+  <si>
     <t>{user_name} ({department}) vừa gửi yêu cầu xin quyền xem/tải tài liệu nội bộ "{doc_name}" (Mã: {doc_code}). Vui lòng phê duyệt cấp quyền.</t>
-  </si>
-  <si>
-    <t>KỊCH BẢN THÔNG BÁO THEO YÊU CẦU TRỌNG TÂM CỦA NGƯỜI DÙNG</t>
-  </si>
-  <si>
-    <t>Chi tiết 5 kịch bản thông báo chính thức tại phân hệ CMS &amp; Điều chỉnh số liệu công bố theo yêu cầu của Vietnam Airlines</t>
-  </si>
-  <si>
-    <t>Phân Hệ / Chức Năng</t>
-  </si>
-  <si>
-    <t>Yêu Cầu Từ Người Dùng</t>
-  </si>
-  <si>
-    <t>Sự Kiện Kích Hoạt (Trigger Event)</t>
-  </si>
-  <si>
-    <t>Người Thực Hiện Thao Tác</t>
-  </si>
-  <si>
-    <t>Nội Dung Hiển Thị Mẫu (In-app Notification)</t>
-  </si>
-  <si>
-    <t>Mức Độ Thông Báo</t>
-  </si>
-  <si>
-    <t>Hành Vi Khi Người Dùng Bấm Vào Thông Báo (Deep Link)</t>
-  </si>
-  <si>
-    <t>Kênh Triển Khai</t>
-  </si>
-  <si>
-    <t>Mức Độ Ưu Tiên</t>
-  </si>
-  <si>
-    <t>PHÂN TÍCH NGHIỆP VỤ &amp; ĐỀ XUẤT BỔ SUNG KỊCH BẢN THÔNG BÁO</t>
-  </si>
-  <si>
-    <t>Đánh giá rủi ro khoảng trống quy trình (Blind Spots), giá trị nghiệp vụ và giải pháp thông báo bổ trợ cho CMS &amp; Điều chỉnh số liệu</t>
-  </si>
-  <si>
-    <t>Kịch Bản Nghiệp Vụ Bổ Sung</t>
-  </si>
-  <si>
-    <t>Rủi Ro Nghiệp Vụ Nếu Thiếu Thông Báo Này (Risk / Pain Point)</t>
-  </si>
-  <si>
-    <t>Giá Trị Mang Lại Cho Vietnam Airlines (Business Value)</t>
-  </si>
-  <si>
-    <t>Hành Động Kích Hoạt &amp; Đối Tượng Nhận Tin</t>
-  </si>
-  <si>
-    <t>Nội Dung Thông Báo Đề Xuất</t>
-  </si>
-  <si>
-    <t>Mức Độ Ưu Tiên Triển Khai</t>
-  </si>
-  <si>
-    <t>Các tổ ban và bộ phận truyền thông không biết phiên bản nào đang là số liệu chính thức được phép trích xuất phục vụ kiểm toán đối ngoại.</t>
-  </si>
-  <si>
-    <t>Minh bạch hóa phiên bản dữ liệu hiện hành, đảm bảo tính duy nhất và nhất quán của số liệu công bố trên toàn hệ thống.</t>
-  </si>
-  <si>
-    <t>Admin kích hoạt bản Active -&gt; Gửi toàn bộ Tổ ban phụ trách &amp; Ban Biên tập báo cáo</t>
-  </si>
-  <si>
-    <t>Yêu cầu khẩn gỡ công bố phiên bản (Unpublish Request)</t>
-  </si>
-  <si>
-    <t>Khi phát hiện số liệu sai sót nghiêm trọng hoặc có thay đổi kiểm toán, nếu không có cơ chế báo khẩn, số liệu sai sẽ tiếp tục hiển thị đối ngoại gây khủng hoảng thông tin.</t>
-  </si>
-  <si>
-    <t>Phản ứng nhanh với sự cố sai lệch số liệu, cho phép thu hồi và tạm ẩn biểu đồ ngay lập tức để rà soát.</t>
-  </si>
-  <si>
-    <t>Tổ ban gửi yêu cầu gỡ công bố -&gt; Gửi Quản trị viên CMS &amp; Lãnh đạo Ban KHPT</t>
-  </si>
-  <si>
-    <t>Từ chối yêu cầu công bố số liệu kèm lý do</t>
-  </si>
-  <si>
-    <t>Chuyên viên tổ ban gửi yêu cầu công bố nhưng không nhận được phản hồi, không biết lý do bị chậm hoặc bị từ chối, gây tắc nghẽn tiến độ đóng kỳ báo cáo.</t>
-  </si>
-  <si>
-    <t>Khép kín chu trình kiểm duyệt (Approval Loop), giúp người nhập dữ liệu nhanh chóng sửa chữa đúng trọng tâm yêu cầu.</t>
-  </si>
-  <si>
-    <t>Admin/Lãnh đạo bấm Từ chối -&gt; Gửi Chuyên viên tổ ban đã tạo yêu cầu</t>
-  </si>
-  <si>
-    <t>Dữ liệu ở các phân hệ nguồn (Nhập liệu thủ công, ERP, Flight Data) bị ai đó sửa đổi ngầm sau khi đã công bố, dẫn đến số liệu công bố vênh với số liệu sổ sách kế toán.</t>
-  </si>
-  <si>
-    <t>Tự động phát hiện bất đồng bộ dữ liệu (Data Integrity Audit), bảo vệ tính pháp lý của báo cáo thường niên.</t>
-  </si>
-  <si>
-    <t>Hệ thống tự động phát hiện lệch -&gt; Gửi Chuyên viên phụ trách chỉ tiêu &amp; Quản trị viên số liệu</t>
-  </si>
-  <si>
-    <t>Thuyết minh giải trình biến động (GRI Disclosure) bị cập nhật nhưng các bên liên quan không nắm được ngữ cảnh phân tích mới.</t>
-  </si>
-  <si>
-    <t>Đồng bộ hóa thông điệp truyền thông giữa số liệu biểu đồ và văn bản phân tích nguyên nhân tăng giảm phát thải.</t>
-  </si>
-  <si>
-    <t>Biên tập viên lưu thuyết minh -&gt; Gửi các Tổ ban liên quan &amp; Ban Truyền thông</t>
-  </si>
-  <si>
-    <t>Các đơn vị chậm trễ nộp báo cáo định kỳ tháng/quý dẫn đến việc cổng Net Zero bị chậm tiến độ cập nhật số liệu mới cho cổ đông và nhà đầu tư.</t>
-  </si>
-  <si>
-    <t>Tự động hóa quy trình đôn đốc tiến độ, giảm thiểu thời gian nhân sự quản trị phải đi nhắc việc thủ công.</t>
-  </si>
-  <si>
-    <t>Hệ thống tự động nhắc ngày 25 hàng tháng -&gt; Gửi Đầu mối nhập liệu của các Tổ ban</t>
-  </si>
-  <si>
-    <t>Thay đổi vị trí biểu đồ trọng điểm vô tình làm đảo lộn cấu trúc logic của báo cáo chuyên môn mà ban phụ trách trụ cột không hay biết.</t>
-  </si>
-  <si>
-    <t>Lưu vết và thông báo thay đổi layout giao diện, giúp ban phụ trách kiểm soát thứ tự ưu tiên truyền thông.</t>
-  </si>
-  <si>
-    <t>Admin kéo thả đổi thứ tự biểu đồ -&gt; Gửi Ban phụ trách Trụ cột &amp; Ban Truyền thông</t>
-  </si>
-  <si>
-    <t>Hệ thống đã cập nhật bộ số liệu mới ra ngoài cổng thông tin công cộng nhưng nội bộ cán bộ công nhân viên không nắm được để truyền thông thống nhất.</t>
-  </si>
-  <si>
-    <t>Tạo sự đồng thuận cao, thông tin kịp thời đến toàn bộ Tổng công ty về thành tựu và chỉ số Net Zero mới nhất.</t>
-  </si>
-  <si>
-    <t>Lãnh đạo bấm Xuất bản Portal -&gt; Gửi Toàn thể người dùng hệ thống ESG VNA</t>
-  </si>
-  <si>
-    <t>Biểu đồ được xuất bản công khai ra ngoài nhưng bị trắng số liệu (Blank chart) hoặc chỉ có dữ liệu cũ của năm ngoái, ảnh hưởng hình ảnh chuyên nghiệp của VNA.</t>
-  </si>
-  <si>
-    <t>Ngăn chặn lỗi hiển thị biểu đồ rỗng trên cổng thông tin đối ngoại, đóng vai trò như chốt kiểm soát chất lượng (Quality Gate).</t>
-  </si>
-  <si>
-    <t>Hệ thống phát hiện thiếu số liệu -&gt; Gửi Quản trị viên CMS &amp; Tổ ban liên quan</t>
-  </si>
-  <si>
-    <t>Người đăng tải không biết tài liệu đã được duyệt hay chưa, dẫn đến việc tải lên trùng lặp hoặc không kịp thời chia sẻ cho đối tác.</t>
-  </si>
-  <si>
-    <t>Rút ngắn vòng quay tài liệu, giúp người nộp tài liệu an tâm rằng văn bản đã được pháp chế/Ban KHPT công nhận lưu kho.</t>
-  </si>
-  <si>
-    <t>Người kiểm duyệt bấm Phê duyệt -&gt; Gửi Người đăng tải tài liệu (Uploader)</t>
-  </si>
-  <si>
-    <t>Tài liệu bị treo không được duyệt mà không rõ nguyên nhân, dẫn đến thất lạc hồ sơ chứng nhận môi trường quan trọng.</t>
-  </si>
-  <si>
-    <t>Phản hồi minh bạch nguyên nhân từ chối (thiếu chữ ký số, sai định dạng, hết hạn) để đơn vị nhanh chóng hoàn thiện hồ sơ.</t>
-  </si>
-  <si>
-    <t>Người kiểm duyệt bấm Từ chối -&gt; Gửi Người đăng tải tài liệu</t>
-  </si>
-  <si>
-    <t>Cán bộ các ban tiếp tục sử dụng các quy chuẩn cũ, biểu mẫu cũ đã lỗi thời do không biết đã có bản cập nhật mới được ban hành.</t>
-  </si>
-  <si>
-    <t>Đảm bảo toàn bộ Tổng công ty luôn áp dụng phiên bản tài liệu chuẩn hóa mới nhất theo chuẩn quốc tế IATA/ICAO.</t>
-  </si>
-  <si>
-    <t>Người quản lý kho cập nhật phiên bản -&gt; Gửi Toàn bộ cán bộ có quyền truy cập</t>
-  </si>
-  <si>
-    <t>Tài liệu bảo mật cao bị người ngoài ban xem trái phép hoặc ngược lại chuyên viên cần dữ liệu phục vụ kiểm toán bị chậm trễ cấp quyền.</t>
-  </si>
-  <si>
-    <t>Quản trị an toàn thông tin theo chuẩn phân quyền tài liệu nội bộ, có vết phê duyệt cấp quyền rõ ràng.</t>
-  </si>
-  <si>
-    <t>User bấm Xin quyền -&gt; Gửi Người sở hữu tài liệu &amp; Admin hệ thống</t>
   </si>
   <si>
     <t>ĐẶC TẢ KỸ THUẬT GIAO DIỆN &amp; TRẢI NGHIỆM THÔNG BÁO (UI/UX SPECIFICATION)</t>
@@ -748,16 +781,13 @@
   </si>
   <si>
     <t>Đã sẵn sàng hook tích hợp trong Settings.tsx</t>
-  </si>
-  <si>
-    <t>[Phê duyệt tài liệu] Tài liệu "{doc_name}" đã được duyệt vào Kho tài liệu PTBV</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -849,8 +879,19 @@
       <color rgb="FFD97706"/>
       <name val="Segoe UI"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8.5"/>
+      <color rgb="FF9A3412"/>
+      <name val="Segoe UI"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -911,8 +952,32 @@
         <bgColor rgb="FFF3E8FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFE0F2FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -935,11 +1000,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -953,9 +1033,6 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -989,13 +1066,58 @@
     <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1008,6 +1130,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1310,7 +1454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1330,58 +1474,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
     </row>
     <row r="2" spans="1:14" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
     </row>
     <row r="3" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="21"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
     </row>
     <row r="4" spans="1:14" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -1429,399 +1573,443 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
+      <c r="A6" s="18">
         <v>1</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="K6" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L6" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="M6" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="N6" s="8" t="s">
+      <c r="N6" s="24" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="9">
+      <c r="A7" s="25">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="J7" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="K7" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="L7" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="M7" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="N7" s="14" t="s">
+      <c r="N7" s="30" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
+      <c r="A8" s="18">
         <v>3</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="K8" s="15" t="s">
+      <c r="K8" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="L8" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="M8" s="6" t="s">
+      <c r="M8" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="N8" s="8" t="s">
+      <c r="N8" s="24" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="9">
+      <c r="A9" s="25">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="J9" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="K9" s="16" t="s">
+      <c r="K9" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="L9" s="12" t="s">
+      <c r="L9" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="M9" s="12" t="s">
+      <c r="M9" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="N9" s="14" t="s">
+      <c r="N9" s="30" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
+      <c r="A10" s="18">
         <v>5</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="K10" s="15" t="s">
+      <c r="K10" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="M10" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="N10" s="8" t="s">
+      <c r="N10" s="24" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="9">
+    <row r="11" spans="1:14" s="45" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="38">
         <v>6</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="42" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="I11" s="40" t="s">
+        <v>74</v>
+      </c>
+      <c r="J11" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="K11" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="L11" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="M11" s="42" t="s">
+        <v>77</v>
+      </c>
+      <c r="N11" s="44" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="18">
+        <v>7</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="K11" s="16" t="s">
+      <c r="D12" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="K12" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="M11" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="N11" s="14" t="s">
+      <c r="L12" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="M12" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="N12" s="24" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="2">
-        <v>7</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" s="4" t="s">
+    <row r="13" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="25">
+        <v>8</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="E12" s="6" t="s">
+      <c r="D13" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="K12" s="7" t="s">
+      <c r="E13" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="H13" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="I13" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="J13" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="K13" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="N12" s="8" t="s">
+      <c r="L13" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="M13" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="N13" s="30" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="9">
-        <v>8</v>
-      </c>
-      <c r="B13" s="3" t="s">
+    <row r="14" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="18">
+        <v>9</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="K14" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="M14" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="N14" s="24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="25">
+        <v>10</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="G15" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="H15" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="I15" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" s="6" t="s">
+      <c r="J15" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="K15" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="L15" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="M15" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="N15" s="30" t="s">
         <v>115</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="K13" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="N13" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="2">
-        <v>9</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="N14" s="18" t="s">
-        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1837,7 +2025,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1856,55 +2044,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
     </row>
     <row r="2" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
+      <c r="A2" s="36" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
     </row>
     <row r="3" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21"/>
+      <c r="A3" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
     </row>
     <row r="4" spans="1:13" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -1915,16 +2103,16 @@
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>10</v>
@@ -1933,19 +2121,19 @@
         <v>11</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="46" customHeight="1" x14ac:dyDescent="0.2">
@@ -1961,10 +2149,10 @@
       <c r="D6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>22</v>
       </c>
       <c r="G6" s="4" t="s">
@@ -1973,60 +2161,60 @@
       <c r="H6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L6" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="M6" s="7" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="9">
+      <c r="A7" s="8">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="K7" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="L7" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="M7" s="14" t="s">
+      <c r="M7" s="13" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2043,10 +2231,10 @@
       <c r="D8" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>44</v>
       </c>
       <c r="G8" s="4" t="s">
@@ -2055,60 +2243,60 @@
       <c r="H8" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J8" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="L8" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="M8" s="8" t="s">
+      <c r="M8" s="7" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="9">
+      <c r="A9" s="8">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="J9" s="16" t="s">
+      <c r="J9" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="K9" s="12" t="s">
+      <c r="K9" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="L9" s="12" t="s">
+      <c r="L9" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="M9" s="14" t="s">
+      <c r="M9" s="13" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2125,10 +2313,10 @@
       <c r="D10" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="5" t="s">
         <v>55</v>
       </c>
       <c r="G10" s="4" t="s">
@@ -2137,19 +2325,60 @@
       <c r="H10" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="J10" s="15" t="s">
+      <c r="J10" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="M10" s="8" t="s">
+      <c r="M10" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="25">
+        <v>6</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="H11" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="I11" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="J11" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L11" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="M11" s="30" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2182,46 +2411,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
     </row>
     <row r="2" spans="1:10" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
+      <c r="A2" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
     </row>
     <row r="3" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
+      <c r="A3" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
     </row>
     <row r="4" spans="1:10" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -2235,25 +2464,25 @@
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.2">
@@ -2261,62 +2490,62 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="I6" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="I6" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="7" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="9">
+      <c r="A7" s="8">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" s="11" t="s">
+      <c r="B7" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="I7" s="7" t="s">
+      <c r="D7" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="J7" s="13" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2325,63 +2554,63 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="I8" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="I8" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="7" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="9">
+      <c r="A9" s="8">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="C9" s="11" t="s">
+      <c r="B9" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="I9" s="15" t="s">
+      <c r="D9" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="I9" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="J9" s="19" t="s">
-        <v>92</v>
+      <c r="J9" s="17" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.2">
@@ -2389,62 +2618,62 @@
         <v>5</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>93</v>
+        <v>154</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="I10" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="I10" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J10" s="18" t="s">
-        <v>92</v>
+      <c r="J10" s="16" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="9">
+      <c r="A11" s="8">
         <v>6</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="C11" s="11" t="s">
+      <c r="B11" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="I11" s="7" t="s">
+      <c r="D11" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="I11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J11" s="14" t="s">
+      <c r="J11" s="13" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2453,62 +2682,62 @@
         <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E12" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="J12" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="F12" s="6" t="s">
+    </row>
+    <row r="13" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="8">
+        <v>8</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="C13" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="H12" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="J12" s="18" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="9">
-        <v>8</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="E13" s="12" t="s">
+      <c r="D13" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="E13" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="F13" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="H13" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="I13" s="16" t="s">
+      <c r="G13" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="I13" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="J13" s="14" t="s">
+      <c r="J13" s="13" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2517,62 +2746,62 @@
         <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>108</v>
+        <v>180</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="I14" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="I14" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J14" s="7" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="9">
+      <c r="A15" s="8">
         <v>10</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="C15" s="11" t="s">
+      <c r="B15" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="I15" s="16" t="s">
+      <c r="D15" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="I15" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="J15" s="13" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2581,63 +2810,63 @@
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>119</v>
+        <v>189</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>31</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="I16" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="I16" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="J16" s="7" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="9">
+      <c r="A17" s="8">
         <v>12</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="C17" s="11" t="s">
+      <c r="B17" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="G17" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="I17" s="13" t="s">
+      <c r="D17" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="I17" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J17" s="19" t="s">
-        <v>92</v>
+      <c r="J17" s="17" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.2">
@@ -2645,31 +2874,31 @@
         <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>130</v>
+        <v>198</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>31</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="I18" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="I18" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J18" s="18" t="s">
-        <v>92</v>
+      <c r="J18" s="16" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -2697,34 +2926,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
     </row>
     <row r="2" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
-        <v>193</v>
-      </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
+      <c r="A2" s="36" t="s">
+        <v>204</v>
+      </c>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
     </row>
     <row r="3" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
+      <c r="A3" s="34" t="s">
+        <v>205</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
     </row>
     <row r="4" spans="1:6" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -2732,19 +2961,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="65" customHeight="1" x14ac:dyDescent="0.2">
@@ -2752,39 +2981,39 @@
         <v>1</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>204</v>
+        <v>211</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="9">
+      <c r="A7" s="8">
         <v>2</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>209</v>
+      <c r="B7" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="65" customHeight="1" x14ac:dyDescent="0.2">
@@ -2792,39 +3021,39 @@
         <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>214</v>
+        <v>221</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="9">
+      <c r="A9" s="8">
         <v>4</v>
       </c>
-      <c r="B9" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>219</v>
+      <c r="B9" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="65" customHeight="1" x14ac:dyDescent="0.2">
@@ -2832,39 +3061,39 @@
         <v>5</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>224</v>
+        <v>231</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="9">
+      <c r="A11" s="8">
         <v>6</v>
       </c>
-      <c r="B11" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>229</v>
+      <c r="B11" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="65" customHeight="1" x14ac:dyDescent="0.2">
@@ -2872,19 +3101,19 @@
         <v>7</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>234</v>
+        <v>241</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>

--- a/images/document/BA DOC/Danh_Sach_Kich_Ban_Thong_Bao_Notification_VNA.xlsx
+++ b/images/document/BA DOC/Danh_Sach_Kich_Ban_Thong_Bao_Notification_VNA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d39b8747432be571/Work/04. Company/Synodus/GOV/01.VNA/VNA/images/document/BA DOC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_93ADAED65B0A42C7C80014FF7B59782981560B81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39C608F0-FBAC-5B40-93F2-2D9938FBE71E}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_97B9AA41F510EF1E63BEC66F1391F846B886D06F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65DAA669-2F63-E641-9071-B8D6D7A56AA4}"/>
   <bookViews>
     <workbookView xWindow="4180" yWindow="500" windowWidth="29420" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,8 +19,8 @@
     <sheet name="4. Quy Chuẩn Kỹ Thuật UI-UX" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Danh Mục Tổng Hợp'!$A$5:$N$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Kịch Bản Yêu Cầu Gốc'!$A$5:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Danh Mục Tổng Hợp'!$A$5:$N$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Kịch Bản Yêu Cầu Gốc'!$A$5:$M$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Đề Xuất Bổ Sung &amp; Phân Tích'!$A$5:$J$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4. Quy Chuẩn Kỹ Thuật UI-UX'!$A$5:$F$12</definedName>
   </definedNames>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="258">
   <si>
     <t>TỔNG CÔNG TY HÀNG KHÔNG VIỆT NAM (VIETNAM AIRLINES) - CỔNG THÔNG TIN NET ZERO &amp; BÁO CÁO PHÁT TRIỂN BỀN VỮNG</t>
   </si>
@@ -100,316 +100,349 @@
     <t>Chuyên viên Tổ ban (Tổ Khai thác, Ban ATCL, Tổ Kỹ thuật, Ban TCNL...)</t>
   </si>
   <si>
+    <t>Người dùng được phân quyền CRUD CMS</t>
+  </si>
+  <si>
+    <t>[Yêu cầu công bố số liệu] {indicator_code} - {indicator_name}</t>
+  </si>
+  <si>
+    <t>{user_name} ({department}) vừa gửi đề nghị công bố phiên bản {version_number} cho biểu đồ/chỉ tiêu "{chart_name}". Vui lòng kiểm tra và duyệt xuất bản trên CMS.</t>
+  </si>
+  <si>
+    <t>Yêu cầu xử lý (Action Required)</t>
+  </si>
+  <si>
+    <t>Điều hướng đến CMS -&gt; Quản lý Biểu đồ Công bố -&gt; Tab Backlog (Highlight thẻ biểu đồ)</t>
+  </si>
+  <si>
+    <t>In-app Quả chuông, Toast popup</t>
+  </si>
+  <si>
+    <t>Cao (P1)</t>
+  </si>
+  <si>
+    <t>NOTIF-CMS-002</t>
+  </si>
+  <si>
+    <t>CMS - Kho tài liệu PTBV</t>
+  </si>
+  <si>
+    <t>Tổ ban thêm tài liệu mới vào Kho tài liệu PTBV</t>
+  </si>
+  <si>
+    <t>Chuyên viên tải tệp lên và nhấn nút "Thêm tài liệu" / "Lưu tài liệu" tại Kho tài liệu PTBV chung</t>
+  </si>
+  <si>
+    <t>Chuyên viên Tổ ban nghiệp vụ (Uploader)</t>
+  </si>
+  <si>
+    <t>Ban Quản trị CMS, Ban KHPT, Cán bộ các Tổ ban trong phạm vi tài liệu</t>
+  </si>
+  <si>
+    <t>[Kho tài liệu PTBV] Tài liệu mới được tải lên: {doc_name}</t>
+  </si>
+  <si>
+    <t>{user_name} ({department}) vừa thêm tài liệu mới "{doc_name}" (Mã: {doc_code}, Loại: {doc_type}, Phạm vi: {scope}) vào Kho tài liệu PTBV chung.</t>
+  </si>
+  <si>
+    <t>Thông tin (Info)</t>
+  </si>
+  <si>
+    <t>Điều hướng đến Kho tài liệu PTBV chung -&gt; Mở modal xem chi tiết tài liệu {doc_code}</t>
+  </si>
+  <si>
+    <t>NOTIF-CMS-008</t>
+  </si>
+  <si>
+    <t>Tổ ban chỉnh sửa lại tài liệu trong 1 bản ghi trong Kho tài liệu PTBV</t>
+  </si>
+  <si>
+    <t>Chuyên viên chỉnh sửa thông tin tài liệu (Tên, mô tả, tệp thay thế, phân loại...) và nhấn nút "Lưu thay đổi" / "Cập nhật" trong 1 bản ghi tại Kho tài liệu PTBV</t>
+  </si>
+  <si>
+    <t>Chuyên viên Tổ ban nghiệp vụ (Editor) / Người sở hữu bản ghi tài liệu</t>
+  </si>
+  <si>
+    <t>[Kho tài liệu PTBV] Cập nhật thông tin tài liệu: {doc_name}</t>
+  </si>
+  <si>
+    <t>Tài liệu "{doc_name}" (Mã: {doc_code}) vừa được {user_name} ({department}) chỉnh sửa, cập nhật thông tin trong Kho tài liệu PTBV chung. Nhấn để xem chi tiết nội dung thay đổi.</t>
+  </si>
+  <si>
+    <t>Điều hướng đến Kho tài liệu PTBV chung -&gt; Mở modal xem chi tiết bản ghi tài liệu {doc_code}</t>
+  </si>
+  <si>
+    <t>In-app Quả chuông, Toast popup, Audit Log</t>
+  </si>
+  <si>
+    <t>NOTIF-CMS-003</t>
+  </si>
+  <si>
+    <t>Tổ ban xóa tài liệu khỏi Kho tài liệu PTBV</t>
+  </si>
+  <si>
+    <t>Người dùng có quyền nhấn biểu tượng Thùng rác và xác nhận xóa tài liệu khỏi danh sách</t>
+  </si>
+  <si>
+    <t>Người sở hữu tài liệu / Quản trị viên Kho tài liệu</t>
+  </si>
+  <si>
+    <t>Ban Quản trị CMS, Ban KHPT, và người đã đăng tài liệu gốc (nếu Admin xóa)</t>
+  </si>
+  <si>
+    <t>[Kho tài liệu PTBV] Tài liệu đã bị xóa: {doc_name}</t>
+  </si>
+  <si>
+    <t>Tài liệu "{doc_name}" (Mã: {doc_code}) đã được gỡ bỏ khỏi Kho tài liệu PTBV chung bởi {user_name} ({department}).</t>
+  </si>
+  <si>
+    <t>Cảnh báo (Warning)</t>
+  </si>
+  <si>
+    <t>Điều hướng đến Kho tài liệu PTBV chung -&gt; Danh sách tài liệu hiện hành</t>
+  </si>
+  <si>
+    <t>In-app Quả chuông, Audit Log</t>
+  </si>
+  <si>
+    <t>NOTIF-ADJ-001</t>
+  </si>
+  <si>
+    <t>Điều chỉnh số liệu công bố</t>
+  </si>
+  <si>
+    <t>Kéo thẻ yêu cầu từ Backlog lên Biểu đồ xuất bản (Sprint) tại CMS</t>
+  </si>
+  <si>
+    <t>Quản trị viên CMS kéo thả thẻ biểu đồ từ khu vực Backlog vào danh sách Biểu đồ xuất bản (Sprint)</t>
+  </si>
+  <si>
+    <t>Quản trị viên CMS (CMS Admin / Ban KHPT)</t>
+  </si>
+  <si>
+    <t>Người dùng phụ trách chỉ tiêu/biểu đồ được xuất bản</t>
+  </si>
+  <si>
+    <t>[Xuất bản Biểu đồ] Biểu đồ {chart_name} đã được chọn xuất bản</t>
+  </si>
+  <si>
+    <t>Biểu đồ "{chart_name}" (Chỉ tiêu {indicator_code}) của {department} đã được {user_name} đưa từ Backlog lên danh sách Biểu đồ xuất bản chính thức trên cổng thông tin Net Zero.</t>
+  </si>
+  <si>
+    <t>Thành công (Success)</t>
+  </si>
+  <si>
+    <t>Điều hướng đến Điều chỉnh số liệu công bố -&gt; Chọn chỉ tiêu {indicator_code} -&gt; Badge "✓ Đang công bố"</t>
+  </si>
+  <si>
+    <t>NOTIF-ADJ-002</t>
+  </si>
+  <si>
+    <t>Xóa thẻ yêu cầu trên Biểu đồ xuất bản tại CMS (Gỡ khỏi xuất bản)</t>
+  </si>
+  <si>
+    <t>Quản trị viên CMS nhấn biểu tượng Xóa (Thùng rác) tại dòng biểu đồ trên bảng Biểu đồ xuất bản</t>
+  </si>
+  <si>
+    <t>Người dùng phụ trách chỉ tiêu/biểu đồ, Người tạo phiên bản công bố</t>
+  </si>
+  <si>
+    <t>[Gỡ xuất bản Biểu đồ] Biểu đồ {chart_name} đã được gỡ khỏi Trang chi tiết</t>
+  </si>
+  <si>
+    <t>Biểu đồ "{chart_name}" (Chỉ tiêu {indicator_code}) đã được {user_name} gỡ khỏi danh sách Biểu đồ xuất bản và chuyển về Backlog. Trạng thái công bố chuyển sang Tạm ẩn.</t>
+  </si>
+  <si>
+    <t>Điều hướng đến Điều chỉnh số liệu công bố -&gt; Chọn chỉ tiêu {indicator_code} -&gt; Tab Quản lý phiên bản</t>
+  </si>
+  <si>
+    <t>NOTIF-CMS-004</t>
+  </si>
+  <si>
+    <t>CMS Admin từ chối thẻ yêu cầu công bố tại Backlog kèm lý do từ chối</t>
+  </si>
+  <si>
+    <t>CMS Admin bấm nút icon Từ chối (XCircle) tại hàng biểu đồ trong Backlog CMS, nhập "Lý do từ chối" vào popup và bấm "Xác nhận từ chối"</t>
+  </si>
+  <si>
+    <t>Quản trị viên CMS (Admin / Ban KHPT)</t>
+  </si>
+  <si>
+    <t>Chuyên viên / User Tổ ban đã bấm "Đề nghị công bố" thẻ yêu cầu đó (Người gửi đề xuất)</t>
+  </si>
+  <si>
+    <t>[Từ chối công bố] {indicator_code} - {chart_name}</t>
+  </si>
+  <si>
+    <t>Yêu cầu công bố biểu đồ "{chart_name}" (Chỉ tiêu {indicator_code}) của bạn đã bị từ chối bởi {admin_name}. Lý do: "{reject_reason}". Vui lòng kiểm tra và hiệu chỉnh lại số liệu.</t>
+  </si>
+  <si>
+    <t>Chuyển tới Điều chỉnh số liệu công bố -&gt; Tự động chọn chỉ tiêu {indicator_code} -&gt; Mở tab Quản lý phiên bản và hiển thị chi tiết lý do từ chối</t>
+  </si>
+  <si>
+    <t>In-app Quả chuông, Toast popup, Email</t>
+  </si>
+  <si>
+    <t>NOTIF-ADJ-003</t>
+  </si>
+  <si>
+    <t>Phân Tích Đề Xuất Bổ Sung</t>
+  </si>
+  <si>
+    <t>Phê duyệt kích hoạt phiên bản chính thức (Active Version)</t>
+  </si>
+  <si>
+    <t>Quản trị viên hoặc Lãnh đạo phê duyệt kích hoạt một phiên bản số liệu sang trạng thái Active (thay thế bản cũ)</t>
+  </si>
+  <si>
+    <t>Admin / Lãnh đạo Ban KHPT</t>
+  </si>
+  <si>
+    <t>Toàn bộ thành viên Tổ ban phụ trách chỉ tiêu, Ban Biên tập báo cáo thường niên</t>
+  </si>
+  <si>
+    <t>[Kích hoạt phiên bản] Đã kích hoạt bản công bố {version_number} - {chart_name}</t>
+  </si>
+  <si>
+    <t>Phiên bản "{version_number} - {version_name}" của biểu đồ "{chart_name}" đã được {user_name} kích hoạt làm bản số liệu công bố chính thức đối ngoại.</t>
+  </si>
+  <si>
+    <t>Điều hướng đến Điều chỉnh số liệu công bố -&gt; Focus vào phiên bản Active của biểu đồ {chart_code}</t>
+  </si>
+  <si>
+    <t>In-app Quả chuông, Email thông báo</t>
+  </si>
+  <si>
+    <t>NOTIF-ADJ-004</t>
+  </si>
+  <si>
+    <t>Tổ ban gửi yêu cầu khẩn đề nghị gỡ công bố phiên bản (Unpublish Request)</t>
+  </si>
+  <si>
+    <t>Tổ ban phát hiện số liệu cần đính chính khẩn cấp và nhấn "Đề nghị gỡ công bố" phiên bản đang Active</t>
+  </si>
+  <si>
+    <t>Chuyên viên Tổ ban phụ trách</t>
+  </si>
+  <si>
+    <t>[Yêu cầu gỡ công bố] Đề nghị gỡ phiên bản {version_number} - {chart_name}</t>
+  </si>
+  <si>
+    <t>{user_name} ({department}) đã gửi yêu cầu khẩn đề nghị gỡ công bố phiên bản {version_number} của biểu đồ "{chart_name}". Lý do: "{reason}".</t>
+  </si>
+  <si>
+    <t>Điều hướng đến CMS -&gt; Mở danh sách phiên bản của biểu đồ và highlight {chart_code}</t>
+  </si>
+  <si>
+    <t>In-app Quả chuông, Toast khẩn cấp</t>
+  </si>
+  <si>
+    <t>NOTIF-DOC-004</t>
+  </si>
+  <si>
+    <t>Phê duyệt tài liệu đưa vào Kho lưu trữ chung thành công</t>
+  </si>
+  <si>
+    <t>Người kiểm duyệt nhấn "Phê duyệt" tài liệu tại màn hình Phê duyệt tài liệu (DocumentApproval.tsx)</t>
+  </si>
+  <si>
+    <t>Người kiểm duyệt tài liệu (Ban KHPT / Admin)</t>
+  </si>
+  <si>
+    <t>Người tải lên tài liệu (Uploader)</t>
+  </si>
+  <si>
+    <t>[Phê duyệt tài liệu] Tài liệu "{doc_name}" đã được duyệt vào Kho tài liệu PTBV</t>
+  </si>
+  <si>
+    <t>Tài liệu "{doc_name}" (Mã: {doc_code}) gửi ngày {submit_date} đã được {approver_name} phê duyệt thành công và đưa vào Kho tài liệu PTBV chung.</t>
+  </si>
+  <si>
+    <t>Điều hướng đến Kho tài liệu PTBV -&gt; Xem tài liệu đã duyệt trong kho chung</t>
+  </si>
+  <si>
+    <t>In-app Quả chuông, Email xác nhận</t>
+  </si>
+  <si>
+    <t>NOTIF-DOC-006</t>
+  </si>
+  <si>
+    <t>Cập nhật phiên bản mới của tài liệu trong Kho PTBV (v1.0 -&gt; v2.0)</t>
+  </si>
+  <si>
+    <t>Người dùng tải tệp thay thế hoặc cập nhật phiên bản tài liệu mới (Semantic Versioning)</t>
+  </si>
+  <si>
+    <t>Người sở hữu tài liệu / Quản trị viên Kho</t>
+  </si>
+  <si>
+    <t>Toàn bộ cán bộ nhân viên có quyền truy cập tài liệu này</t>
+  </si>
+  <si>
+    <t>[Cập nhật phiên bản] Tài liệu "{doc_name}" đã nâng cấp lên bản {doc_version}</t>
+  </si>
+  <si>
+    <t>Tài liệu "{doc_name}" vừa được {user_name} cập nhật phiên bản mới {doc_version} (Ghi chú: {version_notes}). Nhấn để tải về tài liệu mới nhất.</t>
+  </si>
+  <si>
+    <t>Điều hướng đến Kho tài liệu PTBV -&gt; Mở modal Chi tiết tài liệu với bản mới nhất</t>
+  </si>
+  <si>
+    <t>In-app Quả chuông</t>
+  </si>
+  <si>
+    <t>Trung bình (P2)</t>
+  </si>
+  <si>
+    <t>KỊCH BẢN THÔNG BÁO THEO YÊU CẦU TRỌNG TÂM CỦA NGƯỜI DÙNG</t>
+  </si>
+  <si>
+    <t>Chi tiết 7 kịch bản thông báo chính thức tại phân hệ CMS &amp; Điều chỉnh số liệu công bố theo yêu cầu của Vietnam Airlines</t>
+  </si>
+  <si>
+    <t>Phân Hệ / Chức Năng</t>
+  </si>
+  <si>
+    <t>Yêu Cầu Từ Người Dùng</t>
+  </si>
+  <si>
+    <t>Sự Kiện Kích Hoạt (Trigger Event)</t>
+  </si>
+  <si>
+    <t>Người Thực Hiện Thao Tác</t>
+  </si>
+  <si>
+    <t>Nội Dung Hiển Thị Mẫu (In-app Notification)</t>
+  </si>
+  <si>
+    <t>Mức Độ Thông Báo</t>
+  </si>
+  <si>
+    <t>Hành Vi Khi Người Dùng Bấm Vào Thông Báo (Deep Link)</t>
+  </si>
+  <si>
+    <t>Kênh Triển Khai</t>
+  </si>
+  <si>
+    <t>Mức Độ Ưu Tiên</t>
+  </si>
+  <si>
     <t>Ban Quản trị CMS (CMS Admin), Lãnh đạo Ban KHPT phụ trách duyệt</t>
   </si>
   <si>
-    <t>[Yêu cầu công bố số liệu] {indicator_code} - {indicator_name}</t>
-  </si>
-  <si>
-    <t>{user_name} ({department}) vừa gửi đề nghị công bố phiên bản {version_number} cho biểu đồ/chỉ tiêu "{chart_name}". Vui lòng kiểm tra và duyệt xuất bản trên CMS.</t>
-  </si>
-  <si>
-    <t>Yêu cầu xử lý (Action Required)</t>
-  </si>
-  <si>
-    <t>Điều hướng đến CMS -&gt; Quản lý Biểu đồ Công bố -&gt; Tab Backlog (Highlight thẻ biểu đồ)</t>
-  </si>
-  <si>
     <t>In-app Quả chuông, Toast popup, Email duyệt</t>
   </si>
   <si>
-    <t>Cao (P1)</t>
-  </si>
-  <si>
-    <t>NOTIF-CMS-002</t>
-  </si>
-  <si>
-    <t>CMS - Kho tài liệu PTBV</t>
-  </si>
-  <si>
-    <t>Tổ ban thêm tài liệu mới vào Kho tài liệu PTBV</t>
-  </si>
-  <si>
-    <t>Chuyên viên tải tệp lên và nhấn nút "Thêm tài liệu" / "Lưu tài liệu" tại Kho tài liệu PTBV chung</t>
-  </si>
-  <si>
-    <t>Chuyên viên Tổ ban nghiệp vụ (Uploader)</t>
-  </si>
-  <si>
-    <t>Ban Quản trị CMS, Ban KHPT, Cán bộ các Tổ ban trong phạm vi tài liệu</t>
-  </si>
-  <si>
-    <t>[Kho tài liệu PTBV] Tài liệu mới được tải lên: {doc_name}</t>
-  </si>
-  <si>
-    <t>{user_name} ({department}) vừa thêm tài liệu mới "{doc_name}" (Mã: {doc_code}, Loại: {doc_type}, Phạm vi: {scope}) vào Kho tài liệu PTBV chung.</t>
-  </si>
-  <si>
-    <t>Thông tin (Info)</t>
-  </si>
-  <si>
-    <t>Điều hướng đến Kho tài liệu PTBV chung -&gt; Mở modal xem chi tiết tài liệu {doc_code}</t>
-  </si>
-  <si>
-    <t>In-app Quả chuông, Toast popup</t>
-  </si>
-  <si>
-    <t>NOTIF-CMS-003</t>
-  </si>
-  <si>
-    <t>Tổ ban xóa tài liệu khỏi Kho tài liệu PTBV</t>
-  </si>
-  <si>
-    <t>Người dùng có quyền nhấn biểu tượng Thùng rác và xác nhận xóa tài liệu khỏi danh sách</t>
-  </si>
-  <si>
-    <t>Người sở hữu tài liệu / Quản trị viên Kho tài liệu</t>
-  </si>
-  <si>
-    <t>Ban Quản trị CMS, Ban KHPT, và người đã đăng tài liệu gốc (nếu Admin xóa)</t>
-  </si>
-  <si>
-    <t>[Kho tài liệu PTBV] Tài liệu đã bị xóa: {doc_name}</t>
-  </si>
-  <si>
-    <t>Tài liệu "{doc_name}" (Mã: {doc_code}) đã được gỡ bỏ khỏi Kho tài liệu PTBV chung bởi {user_name} ({department}).</t>
-  </si>
-  <si>
-    <t>Cảnh báo (Warning)</t>
-  </si>
-  <si>
-    <t>Điều hướng đến Kho tài liệu PTBV chung -&gt; Danh sách tài liệu hiện hành</t>
-  </si>
-  <si>
-    <t>In-app Quả chuông, Audit Log</t>
-  </si>
-  <si>
-    <t>NOTIF-ADJ-001</t>
-  </si>
-  <si>
-    <t>Điều chỉnh số liệu công bố</t>
-  </si>
-  <si>
-    <t>Kéo thẻ yêu cầu từ Backlog lên Biểu đồ xuất bản (Sprint) tại CMS</t>
-  </si>
-  <si>
-    <t>Quản trị viên CMS kéo thả thẻ biểu đồ từ khu vực Backlog vào danh sách Biểu đồ xuất bản (Sprint)</t>
-  </si>
-  <si>
-    <t>Quản trị viên CMS (CMS Admin / Ban KHPT)</t>
+    <t>Chuyên viên/Người sở hữu tài liệu chỉnh sửa thông tin (Tên tài liệu, mô tả, phân loại, tệp đính kèm thay thế, phạm vi công bố...) và nhấn nút "Lưu thay đổi" / "Cập nhật" trong 1 bản ghi tại Kho tài liệu PTBV</t>
   </si>
   <si>
     <t>Chuyên viên và Lãnh đạo Tổ ban phụ trách chỉ tiêu/biểu đồ được xuất bản</t>
   </si>
   <si>
-    <t>[Xuất bản Biểu đồ] Biểu đồ {chart_name} đã được chọn xuất bản</t>
-  </si>
-  <si>
-    <t>Biểu đồ "{chart_name}" (Chỉ tiêu {indicator_code}) của {department} đã được {user_name} đưa từ Backlog lên danh sách Biểu đồ xuất bản chính thức trên cổng thông tin Net Zero.</t>
-  </si>
-  <si>
-    <t>Thành công (Success)</t>
-  </si>
-  <si>
-    <t>Điều hướng đến Điều chỉnh số liệu công bố -&gt; Chọn chỉ tiêu {indicator_code} -&gt; Badge "✓ Đang công bố"</t>
-  </si>
-  <si>
-    <t>NOTIF-ADJ-002</t>
-  </si>
-  <si>
-    <t>Xóa thẻ yêu cầu trên Biểu đồ xuất bản tại CMS (Gỡ khỏi xuất bản)</t>
-  </si>
-  <si>
-    <t>Quản trị viên CMS nhấn biểu tượng Xóa (Thùng rác) tại dòng biểu đồ trên bảng Biểu đồ xuất bản</t>
-  </si>
-  <si>
     <t>Tổ ban phụ trách chỉ tiêu/biểu đồ, Người tạo phiên bản công bố</t>
   </si>
   <si>
-    <t>[Gỡ xuất bản Biểu đồ] Biểu đồ {chart_name} đã được gỡ khỏi Trang chi tiết</t>
-  </si>
-  <si>
-    <t>Biểu đồ "{chart_name}" (Chỉ tiêu {indicator_code}) đã được {user_name} gỡ khỏi danh sách Biểu đồ xuất bản và chuyển về Backlog. Trạng thái công bố chuyển sang Tạm ẩn.</t>
-  </si>
-  <si>
-    <t>Điều hướng đến Điều chỉnh số liệu công bố -&gt; Chọn chỉ tiêu {indicator_code} -&gt; Tab Quản lý phiên bản</t>
-  </si>
-  <si>
-    <t>NOTIF-CMS-004</t>
-  </si>
-  <si>
     <t>CMS - Quản lý Biểu đồ Công bố &amp; Điều chỉnh số liệu</t>
-  </si>
-  <si>
-    <t>CMS Admin từ chối thẻ yêu cầu công bố tại Backlog kèm lý do từ chối</t>
-  </si>
-  <si>
-    <t>CMS Admin bấm nút icon Từ chối (XCircle) tại hàng biểu đồ trong Backlog CMS, nhập "Lý do từ chối" vào popup và bấm "Xác nhận từ chối"</t>
-  </si>
-  <si>
-    <t>Quản trị viên CMS (Admin / Ban KHPT)</t>
-  </si>
-  <si>
-    <t>Chuyên viên / User Tổ ban đã bấm "Đề nghị công bố" thẻ yêu cầu đó (Người gửi đề xuất)</t>
-  </si>
-  <si>
-    <t>[Từ chối công bố] {indicator_code} - {chart_name}</t>
-  </si>
-  <si>
-    <t>Yêu cầu công bố biểu đồ "{chart_name}" (Chỉ tiêu {indicator_code}) của bạn đã bị từ chối bởi {admin_name}. Lý do: "{reject_reason}". Vui lòng kiểm tra và hiệu chỉnh lại số liệu.</t>
-  </si>
-  <si>
-    <t>Chuyển tới Điều chỉnh số liệu công bố -&gt; Tự động chọn chỉ tiêu {indicator_code} -&gt; Mở tab Quản lý phiên bản và hiển thị chi tiết lý do từ chối</t>
-  </si>
-  <si>
-    <t>In-app Quả chuông, Toast popup, Email</t>
-  </si>
-  <si>
-    <t>NOTIF-ADJ-003</t>
-  </si>
-  <si>
-    <t>Phân Tích Đề Xuất Bổ Sung</t>
-  </si>
-  <si>
-    <t>Phê duyệt kích hoạt phiên bản chính thức (Active Version)</t>
-  </si>
-  <si>
-    <t>Quản trị viên hoặc Lãnh đạo phê duyệt kích hoạt một phiên bản số liệu sang trạng thái Active (thay thế bản cũ)</t>
-  </si>
-  <si>
-    <t>Admin / Lãnh đạo Ban KHPT</t>
-  </si>
-  <si>
-    <t>Toàn bộ thành viên Tổ ban phụ trách chỉ tiêu, Ban Biên tập báo cáo thường niên</t>
-  </si>
-  <si>
-    <t>[Kích hoạt phiên bản] Đã kích hoạt bản công bố {version_number} - {chart_name}</t>
-  </si>
-  <si>
-    <t>Phiên bản "{version_number} - {version_name}" của biểu đồ "{chart_name}" đã được {user_name} kích hoạt làm bản số liệu công bố chính thức đối ngoại.</t>
-  </si>
-  <si>
-    <t>Điều hướng đến Điều chỉnh số liệu công bố -&gt; Focus vào phiên bản Active của biểu đồ {chart_code}</t>
-  </si>
-  <si>
-    <t>In-app Quả chuông, Email thông báo</t>
-  </si>
-  <si>
-    <t>NOTIF-ADJ-004</t>
-  </si>
-  <si>
-    <t>Tổ ban gửi yêu cầu khẩn đề nghị gỡ công bố phiên bản (Unpublish Request)</t>
-  </si>
-  <si>
-    <t>Tổ ban phát hiện số liệu cần đính chính khẩn cấp và nhấn "Đề nghị gỡ công bố" phiên bản đang Active</t>
-  </si>
-  <si>
-    <t>Chuyên viên Tổ ban phụ trách</t>
-  </si>
-  <si>
-    <t>Quản trị viên CMS, Lãnh đạo Ban KHPT</t>
-  </si>
-  <si>
-    <t>[Yêu cầu gỡ công bố] Đề nghị gỡ phiên bản {version_number} - {chart_name}</t>
-  </si>
-  <si>
-    <t>{user_name} ({department}) đã gửi yêu cầu khẩn đề nghị gỡ công bố phiên bản {version_number} của biểu đồ "{chart_name}". Lý do: "{reason}".</t>
-  </si>
-  <si>
-    <t>Điều hướng đến Điều chỉnh số liệu công bố -&gt; Mở danh sách phiên bản của biểu đồ {chart_code}</t>
-  </si>
-  <si>
-    <t>In-app Quả chuông, Toast khẩn cấp, Email</t>
-  </si>
-  <si>
-    <t>NOTIF-DOC-004</t>
-  </si>
-  <si>
-    <t>Phê duyệt tài liệu đưa vào Kho lưu trữ chung thành công</t>
-  </si>
-  <si>
-    <t>Người kiểm duyệt nhấn "Phê duyệt" tài liệu tại màn hình Phê duyệt tài liệu (DocumentApproval.tsx)</t>
-  </si>
-  <si>
-    <t>Người kiểm duyệt tài liệu (Ban KHPT / Admin)</t>
-  </si>
-  <si>
-    <t>Người tải lên tài liệu (Uploader)</t>
-  </si>
-  <si>
-    <t>[Phê duyệt tài liệu] Tài liệu "{doc_name}" đã được duyệt vào Kho tài liệu PTBV</t>
-  </si>
-  <si>
-    <t>Tài liệu "{doc_name}" (Mã: {doc_code}) gửi ngày {submit_date} đã được {approver_name} phê duyệt thành công và đưa vào Kho tài liệu PTBV chung.</t>
-  </si>
-  <si>
-    <t>Điều hướng đến Kho tài liệu PTBV -&gt; Xem tài liệu đã duyệt trong kho chung</t>
-  </si>
-  <si>
-    <t>In-app Quả chuông, Email xác nhận</t>
-  </si>
-  <si>
-    <t>NOTIF-DOC-006</t>
-  </si>
-  <si>
-    <t>Cập nhật phiên bản mới của tài liệu trong Kho PTBV (v1.0 -&gt; v2.0)</t>
-  </si>
-  <si>
-    <t>Người dùng tải tệp thay thế hoặc cập nhật phiên bản tài liệu mới (Semantic Versioning)</t>
-  </si>
-  <si>
-    <t>Người sở hữu tài liệu / Quản trị viên Kho</t>
-  </si>
-  <si>
-    <t>Toàn bộ cán bộ nhân viên có quyền truy cập tài liệu này</t>
-  </si>
-  <si>
-    <t>[Cập nhật phiên bản] Tài liệu "{doc_name}" đã nâng cấp lên bản {doc_version}</t>
-  </si>
-  <si>
-    <t>Tài liệu "{doc_name}" vừa được {user_name} cập nhật phiên bản mới {doc_version} (Ghi chú: {version_notes}). Nhấn để tải về tài liệu mới nhất.</t>
-  </si>
-  <si>
-    <t>Điều hướng đến Kho tài liệu PTBV -&gt; Mở modal Chi tiết tài liệu với bản mới nhất</t>
-  </si>
-  <si>
-    <t>In-app Quả chuông</t>
-  </si>
-  <si>
-    <t>Trung bình (P2)</t>
-  </si>
-  <si>
-    <t>KỊCH BẢN THÔNG BÁO THEO YÊU CẦU TRỌNG TÂM CỦA NGƯỜI DÙNG</t>
-  </si>
-  <si>
-    <t>Chi tiết 6 kịch bản thông báo chính thức tại phân hệ CMS &amp; Điều chỉnh số liệu công bố theo yêu cầu của Vietnam Airlines</t>
-  </si>
-  <si>
-    <t>Phân Hệ / Chức Năng</t>
-  </si>
-  <si>
-    <t>Yêu Cầu Từ Người Dùng</t>
-  </si>
-  <si>
-    <t>Sự Kiện Kích Hoạt (Trigger Event)</t>
-  </si>
-  <si>
-    <t>Người Thực Hiện Thao Tác</t>
-  </si>
-  <si>
-    <t>Nội Dung Hiển Thị Mẫu (In-app Notification)</t>
-  </si>
-  <si>
-    <t>Mức Độ Thông Báo</t>
-  </si>
-  <si>
-    <t>Hành Vi Khi Người Dùng Bấm Vào Thông Báo (Deep Link)</t>
-  </si>
-  <si>
-    <t>Kênh Triển Khai</t>
-  </si>
-  <si>
-    <t>Mức Độ Ưu Tiên</t>
   </si>
   <si>
     <t>PHÂN TÍCH NGHIỆP VỤ &amp; ĐỀ XUẤT BỔ SUNG KỊCH BẢN THÔNG BÁO</t>
@@ -781,13 +814,16 @@
   </si>
   <si>
     <t>Đã sẵn sàng hook tích hợp trong Settings.tsx</t>
+  </si>
+  <si>
+    <t>Ban Quản trị CMS, Ban KHPT, và người đã đăng tài liệu gốc</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -797,33 +833,40 @@
     </font>
     <font>
       <b/>
-      <sz val="8.5"/>
+      <sz val="8"/>
       <color rgb="FF6B7280"/>
       <name val="Segoe UI"/>
     </font>
     <font>
       <b/>
-      <sz val="13.5"/>
+      <sz val="13"/>
       <color rgb="FF003B46"/>
       <name val="Segoe UI"/>
     </font>
     <font>
       <i/>
-      <sz val="9.5"/>
+      <sz val="9"/>
       <color rgb="FF4B5563"/>
       <name val="Segoe UI"/>
     </font>
     <font>
       <b/>
-      <sz val="9.5"/>
+      <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Segoe UI"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF005F6E"/>
       <name val="Consolas"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -833,13 +876,13 @@
     </font>
     <font>
       <b/>
-      <sz val="8.5"/>
+      <sz val="8"/>
       <color rgb="FF0369A1"/>
       <name val="Segoe UI"/>
     </font>
     <font>
       <b/>
-      <sz val="8.5"/>
+      <sz val="8"/>
       <color rgb="FF991B1B"/>
       <name val="Segoe UI"/>
     </font>
@@ -851,43 +894,31 @@
     </font>
     <font>
       <b/>
-      <sz val="8.5"/>
+      <sz val="8"/>
       <color rgb="FF1E40AF"/>
       <name val="Segoe UI"/>
     </font>
     <font>
       <b/>
-      <sz val="8.5"/>
-      <color rgb="FF92400E"/>
-      <name val="Segoe UI"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8.5"/>
+      <sz val="8"/>
       <color rgb="FF166534"/>
       <name val="Segoe UI"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
-      <sz val="8.5"/>
-      <color rgb="FF6B21A8"/>
+      <sz val="8"/>
+      <color rgb="FF92400E"/>
       <name val="Segoe UI"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFD97706"/>
-      <name val="Segoe UI"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8.5"/>
-      <color rgb="FF9A3412"/>
       <name val="Segoe UI"/>
     </font>
   </fonts>
@@ -901,13 +932,37 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF005F6E"/>
-        <bgColor rgb="FF005F6E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2FE"/>
-        <bgColor rgb="FFE0F2FE"/>
+        <fgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FAFB"/>
+        <bgColor rgb="FFF9FAFB"/>
       </patternFill>
     </fill>
     <fill>
@@ -918,20 +973,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8FAFC"/>
-        <bgColor rgb="FFF8FAFC"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDBEAFE"/>
         <bgColor rgb="FFDBEAFE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -948,36 +997,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF3E8FF"/>
-        <bgColor rgb="FFF3E8FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFE0F2FE"/>
         <bgColor rgb="FFE0F2FE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFEE2E2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1000,125 +1025,119 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD1D5DB"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD1D5DB"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD1D5DB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD1D5DB"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1130,34 +1149,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1244,6 +1241,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1278,6 +1276,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1312,20 +1311,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1447,17 +1442,56 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
@@ -1466,69 +1500,70 @@
     <col min="7" max="7" width="24" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
     <col min="9" max="9" width="34" customWidth="1"/>
-    <col min="10" max="10" width="52" customWidth="1"/>
+    <col min="10" max="10" width="42.1640625" customWidth="1"/>
     <col min="11" max="11" width="20" customWidth="1"/>
     <col min="12" max="12" width="36" customWidth="1"/>
     <col min="13" max="13" width="24" customWidth="1"/>
     <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="15" max="24" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-    </row>
-    <row r="2" spans="1:14" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="36" t="s">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+    </row>
+    <row r="2" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-    </row>
-    <row r="3" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="34" t="s">
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+    </row>
+    <row r="3" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="35"/>
-    </row>
-    <row r="4" spans="1:14" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="38"/>
+    </row>
+    <row r="4" spans="1:14" ht="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -1654,7 +1689,7 @@
         <v>39</v>
       </c>
       <c r="M7" s="28" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="N7" s="30" t="s">
         <v>29</v>
@@ -1665,7 +1700,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>31</v>
@@ -1674,31 +1709,31 @@
         <v>19</v>
       </c>
       <c r="E8" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="G8" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="22" t="s">
+      <c r="H8" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="J8" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="I8" s="20" t="s">
+      <c r="K8" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="L8" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="J8" s="22" t="s">
+      <c r="M8" s="22" t="s">
         <v>47</v>
-      </c>
-      <c r="K8" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="L8" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="M8" s="22" t="s">
-        <v>50</v>
       </c>
       <c r="N8" s="24" t="s">
         <v>29</v>
@@ -1709,40 +1744,40 @@
         <v>4</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>19</v>
       </c>
       <c r="E9" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="I9" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="J9" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="G9" s="28" t="s">
+      <c r="K9" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="H9" s="27" t="s">
+      <c r="L9" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="I9" s="27" t="s">
+      <c r="M9" s="28" t="s">
         <v>57</v>
-      </c>
-      <c r="J9" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="K9" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="L9" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="M9" s="28" t="s">
-        <v>40</v>
       </c>
       <c r="N9" s="30" t="s">
         <v>29</v>
@@ -1753,86 +1788,86 @@
         <v>5</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D10" s="21" t="s">
         <v>19</v>
       </c>
       <c r="E10" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="F10" s="22" t="s">
+      <c r="H10" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="G10" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="H10" s="20" t="s">
+      <c r="I10" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="I10" s="20" t="s">
+      <c r="J10" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="J10" s="22" t="s">
+      <c r="K10" s="32" t="s">
         <v>66</v>
-      </c>
-      <c r="K10" s="31" t="s">
-        <v>48</v>
       </c>
       <c r="L10" s="22" t="s">
         <v>67</v>
       </c>
       <c r="M10" s="22" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="N10" s="24" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:14" s="45" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="38">
+    <row r="11" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="25">
         <v>6</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="D11" s="41" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="42" t="s">
+      <c r="F11" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="F11" s="42" t="s">
+      <c r="G11" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="H11" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="42" t="s">
+      <c r="I11" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="H11" s="40" t="s">
+      <c r="J11" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="I11" s="40" t="s">
+      <c r="K11" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="L11" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="J11" s="42" t="s">
-        <v>75</v>
-      </c>
-      <c r="K11" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" s="42" t="s">
-        <v>76</v>
-      </c>
-      <c r="M11" s="42" t="s">
-        <v>77</v>
-      </c>
-      <c r="N11" s="44" t="s">
+      <c r="M11" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="N11" s="30" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1841,40 +1876,40 @@
         <v>7</v>
       </c>
       <c r="B12" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C12" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="33" t="s">
+      <c r="H12" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="I12" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="J12" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="K12" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="L12" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="H12" s="20" t="s">
+      <c r="M12" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="I12" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="J12" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K12" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="L12" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="M12" s="22" t="s">
-        <v>87</v>
       </c>
       <c r="N12" s="24" t="s">
         <v>29</v>
@@ -1885,40 +1920,40 @@
         <v>8</v>
       </c>
       <c r="B13" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="C13" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>79</v>
-      </c>
-      <c r="E13" s="28" t="s">
+      <c r="H13" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="I13" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="G13" s="28" t="s">
+      <c r="J13" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="H13" s="27" t="s">
+      <c r="K13" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="L13" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="I13" s="27" t="s">
+      <c r="M13" s="28" t="s">
         <v>93</v>
-      </c>
-      <c r="J13" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="K13" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="L13" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="M13" s="28" t="s">
-        <v>96</v>
       </c>
       <c r="N13" s="30" t="s">
         <v>29</v>
@@ -1929,40 +1964,40 @@
         <v>9</v>
       </c>
       <c r="B14" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="G14" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="C14" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="33" t="s">
-        <v>79</v>
-      </c>
-      <c r="E14" s="22" t="s">
+      <c r="H14" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="J14" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="K14" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="M14" s="22" t="s">
         <v>101</v>
-      </c>
-      <c r="I14" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="J14" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="K14" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="L14" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="M14" s="22" t="s">
-        <v>105</v>
       </c>
       <c r="N14" s="24" t="s">
         <v>29</v>
@@ -1973,62 +2008,107 @@
         <v>10</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C15" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="33" t="s">
-        <v>79</v>
+      <c r="D15" s="31" t="s">
+        <v>85</v>
       </c>
       <c r="E15" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="G15" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="H15" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="I15" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="F15" s="28" t="s">
+      <c r="J15" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="G15" s="28" t="s">
+      <c r="K15" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="L15" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="H15" s="27" t="s">
+      <c r="M15" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="I15" s="27" t="s">
+      <c r="N15" s="30" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="48" x14ac:dyDescent="0.2">
+      <c r="A16" s="18">
+        <v>11</v>
+      </c>
+      <c r="B16" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="J15" s="28" t="s">
+      <c r="C16" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="K15" s="29" t="s">
+      <c r="F16" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="H16" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="I16" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="K16" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="L15" s="28" t="s">
-        <v>113</v>
-      </c>
-      <c r="M15" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="N15" s="30" t="s">
-        <v>115</v>
+      <c r="L16" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="M16" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="N16" s="24" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:N14" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A5:N16" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="3">
     <mergeCell ref="A3:N3"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
@@ -2037,65 +2117,66 @@
     <col min="7" max="7" width="24" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
     <col min="9" max="9" width="34" customWidth="1"/>
-    <col min="10" max="10" width="52" customWidth="1"/>
+    <col min="10" max="10" width="42.1640625" customWidth="1"/>
     <col min="11" max="11" width="20" customWidth="1"/>
     <col min="12" max="12" width="36" customWidth="1"/>
     <col min="13" max="13" width="24" customWidth="1"/>
+    <col min="14" max="24" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-    </row>
-    <row r="2" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-    </row>
-    <row r="3" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="34" t="s">
-        <v>117</v>
-      </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
-    </row>
-    <row r="4" spans="1:13" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+    </row>
+    <row r="2" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+    </row>
+    <row r="3" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
+    </row>
+    <row r="4" spans="1:13" ht="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -2103,16 +2184,16 @@
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>10</v>
@@ -2121,275 +2202,317 @@
         <v>11</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="33">
         <v>1</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="4" t="s">
+      <c r="G6" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="H6" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="L6" s="5" t="s">
+      <c r="L6" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="M6" s="24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="35">
+        <v>2</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="K7" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="L7" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="M7" s="30" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="8">
-        <v>2</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="10" t="s">
+    <row r="8" spans="1:13" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="33">
+        <v>3</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="10" t="s">
+      <c r="D8" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="F8" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="J7" s="12" t="s">
+      <c r="H8" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="J8" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="K7" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="M7" s="13" t="s">
+      <c r="K8" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="L8" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="M8" s="24" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
-        <v>3</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="4" t="s">
+    <row r="9" spans="1:13" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="35">
+        <v>4</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="K8" s="5" t="s">
+      <c r="D9" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="E9" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="M8" s="7" t="s">
+      <c r="F9" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="K9" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="L9" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="M9" s="30" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="8">
-        <v>4</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="I9" s="11" t="s">
+    <row r="10" spans="1:13" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="33">
+        <v>5</v>
+      </c>
+      <c r="B10" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="J9" s="15" t="s">
+      <c r="C10" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="D10" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="L9" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="M9" s="13" t="s">
+      <c r="E10" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="I10" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="J10" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="K10" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="L10" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="M10" s="24" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
-        <v>5</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="25">
+    <row r="11" spans="1:13" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="35">
         <v>6</v>
       </c>
       <c r="B11" s="26" t="s">
         <v>68</v>
       </c>
       <c r="C11" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="E11" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="E11" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="F11" s="28" t="s">
+      <c r="F11" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="H11" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="I11" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="J11" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="27" t="s">
-        <v>73</v>
-      </c>
-      <c r="H11" s="27" t="s">
+      <c r="K11" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="I11" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="J11" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="K11" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="L11" s="28" t="s">
-        <v>77</v>
+      <c r="L11" s="36" t="s">
+        <v>28</v>
       </c>
       <c r="M11" s="30" t="s">
         <v>29</v>
       </c>
     </row>
+    <row r="12" spans="1:13" ht="112" x14ac:dyDescent="0.2">
+      <c r="A12" s="18">
+        <v>7</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="H12" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="M12" s="24" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:M10" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A5:M12" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="3">
     <mergeCell ref="A3:M3"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
@@ -2398,62 +2521,63 @@
   <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
     <col min="7" max="7" width="34" customWidth="1"/>
-    <col min="8" max="8" width="46" customWidth="1"/>
+    <col min="8" max="8" width="42.1640625" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="24" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-    </row>
-    <row r="2" spans="1:10" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-    </row>
-    <row r="3" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-    </row>
-    <row r="4" spans="1:10" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+    </row>
+    <row r="2" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="39" t="s">
+        <v>138</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+    </row>
+    <row r="3" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+    </row>
+    <row r="4" spans="1:10" ht="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -2464,441 +2588,441 @@
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
+      <c r="A6" s="11">
         <v>1</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="I6" s="15" t="s">
+      <c r="B6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="D6" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J6" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="8">
+      <c r="A7" s="13">
         <v>2</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="H7" s="11" t="s">
+      <c r="B7" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="C7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="9" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
+      <c r="A8" s="11">
         <v>3</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" s="7" t="s">
+      <c r="B8" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="8">
+      <c r="A9" s="13">
         <v>4</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" s="17" t="s">
-        <v>115</v>
+      <c r="B9" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
+      <c r="A10" s="11">
         <v>5</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="I10" s="12" t="s">
+      <c r="B10" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="I10" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="J10" s="16" t="s">
-        <v>115</v>
+      <c r="J10" s="17" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="8">
+      <c r="A11" s="13">
         <v>6</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="I11" s="6" t="s">
+      <c r="B11" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J11" s="13" t="s">
+      <c r="J11" s="9" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="2">
+      <c r="A12" s="11">
         <v>7</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C12" s="4" t="s">
+      <c r="B12" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="I12" s="12" t="s">
+      <c r="D12" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="I12" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="J12" s="16" t="s">
-        <v>172</v>
+      <c r="J12" s="17" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="8">
+      <c r="A13" s="13">
         <v>8</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="I13" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="J13" s="13" t="s">
+      <c r="B13" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J13" s="9" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="2">
+      <c r="A14" s="11">
         <v>9</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="B14" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="I14" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="J14" s="7" t="s">
+      <c r="D14" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="J14" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="8">
+      <c r="A15" s="13">
         <v>10</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C15" s="10" t="s">
+      <c r="B15" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="H15" s="11" t="s">
+      <c r="D15" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="I15" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="J15" s="13" t="s">
+      <c r="E15" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J15" s="9" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="2">
+      <c r="A16" s="11">
         <v>11</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C16" s="4" t="s">
+      <c r="B16" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="I16" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="J16" s="7" t="s">
+      <c r="D16" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="J16" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="8">
+      <c r="A17" s="13">
         <v>12</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="C17" s="10" t="s">
+      <c r="B17" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="H17" s="11" t="s">
+      <c r="D17" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="E17" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="I17" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="J17" s="17" t="s">
-        <v>115</v>
+      <c r="J17" s="16" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="2">
+      <c r="A18" s="11">
         <v>13</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C18" s="4" t="s">
+      <c r="B18" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="I18" s="6" t="s">
+      <c r="D18" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="I18" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J18" s="16" t="s">
-        <v>115</v>
+      <c r="J18" s="17" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -2908,7 +3032,8 @@
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
@@ -2917,203 +3042,204 @@
   <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="38" customWidth="1"/>
-    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="4" max="4" width="42.1640625" customWidth="1"/>
     <col min="5" max="5" width="32" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="7" max="24" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-    </row>
-    <row r="2" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="36" t="s">
-        <v>204</v>
-      </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-    </row>
-    <row r="3" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="34" t="s">
-        <v>205</v>
-      </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-    </row>
-    <row r="4" spans="1:6" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+    </row>
+    <row r="2" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+    </row>
+    <row r="3" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="37" t="s">
+        <v>216</v>
+      </c>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+    </row>
+    <row r="4" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="11">
         <v>1</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="8">
+      <c r="B6" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="13">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
+      <c r="B7" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="11">
         <v>3</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="8">
+      <c r="B8" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="13">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
+      <c r="B9" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="11">
         <v>5</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="8">
+      <c r="B10" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="13">
         <v>6</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="2">
+      <c r="B11" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="11">
         <v>7</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>245</v>
+      <c r="B12" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -3123,6 +3249,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>